--- a/database/controller_excel/Baja FO-DSP BAJA.xlsx
+++ b/database/controller_excel/Baja FO-DSP BAJA.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DSPT\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Inventario_TI\database\controller_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -51,16 +51,13 @@
   </si>
   <si>
     <r>
-      <t>☐</t>
-    </r>
-    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Narrow"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t>☐</t>
     </r>
     <r>
       <rPr>
@@ -70,8 +67,85 @@
         <rFont val="Arial Narrow"/>
         <family val="2"/>
       </rPr>
-      <t>6.-Reubicación de instalación o pozo</t>
+      <t xml:space="preserve"> 5.- Otro:</t>
     </r>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>TIPO</t>
+  </si>
+  <si>
+    <t>ACTIVO FIJO</t>
+  </si>
+  <si>
+    <t>LOTE</t>
+  </si>
+  <si>
+    <t>ÁREA</t>
+  </si>
+  <si>
+    <t>DESCRIPCIÓN</t>
+  </si>
+  <si>
+    <t>En el caso de extravío del activo fijo, indicar lo siguiente:</t>
+  </si>
+  <si>
+    <t>Monto de descuento al empleador:</t>
+  </si>
+  <si>
+    <t>No. de quincenas a descontar:</t>
+  </si>
+  <si>
+    <r>
+      <t>Tipo de activo fijo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>: (1) Mobiliario y equipo de oficina, (2) Equipo de Cómputo, (3) Maquinaria y equipos auxiliar, (4) Otros</t>
+    </r>
+  </si>
+  <si>
+    <t>Para el caso de reubicación pozos, de oficinas operativas o administrativas se deberá especificar la nueva dirección,</t>
+  </si>
+  <si>
+    <t>ubicación o nombre del nuevo pozo:</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Emitió</t>
+  </si>
+  <si>
+    <t>Supervisó</t>
+  </si>
+  <si>
+    <t>Vo. Bo.</t>
+  </si>
+  <si>
+    <t>Autorizó</t>
+  </si>
+  <si>
+    <t>Analisata/Supervisor</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>Coordinador Supervisor de Área</t>
+  </si>
+  <si>
+    <t>Coordinador / Supervisor de Infromación Financiera</t>
+  </si>
+  <si>
+    <t>Gerencia Facultad</t>
   </si>
   <si>
     <r>
@@ -94,16 +168,7 @@
         <rFont val="Arial Narrow"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">            </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-      </rPr>
-      <t>☐</t>
+      <t xml:space="preserve">            ☐</t>
     </r>
     <r>
       <rPr>
@@ -122,16 +187,7 @@
         <rFont val="Arial Narrow"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">             </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-      </rPr>
-      <t>☐</t>
+      <t xml:space="preserve">             ☐</t>
     </r>
     <r>
       <rPr>
@@ -150,25 +206,7 @@
         <rFont val="Arial Narrow"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">               </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-      </rPr>
-      <t>☐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
+      <t xml:space="preserve">               ☐  </t>
     </r>
     <r>
       <rPr>
@@ -183,13 +221,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>☐</t>
+      <t xml:space="preserve">☐ </t>
     </r>
     <r>
       <rPr>
@@ -199,101 +231,16 @@
         <rFont val="Arial Narrow"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> 5.- Otro:</t>
+      <t>6.-Reubicación de instalación o pozo</t>
     </r>
-  </si>
-  <si>
-    <t>ITEM</t>
-  </si>
-  <si>
-    <t>TIPO</t>
-  </si>
-  <si>
-    <t>ACTIVO FIJO</t>
-  </si>
-  <si>
-    <t>LOTE</t>
-  </si>
-  <si>
-    <t>ÁREA</t>
-  </si>
-  <si>
-    <t>DESCRIPCIÓN</t>
-  </si>
-  <si>
-    <t>En el caso de extravío del activo fijo, indicar lo siguiente:</t>
-  </si>
-  <si>
-    <t>Monto de descuento al empleador:</t>
-  </si>
-  <si>
-    <t>No. de quincenas a descontar:</t>
-  </si>
-  <si>
-    <r>
-      <t>Tipo de activo fijo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>: (1) Mobiliario y equipo de oficina, (2) Equipo de Cómputo, (3) Maquinaria y equipos auxiliar, (4) Otros</t>
-    </r>
-  </si>
-  <si>
-    <t>Para el caso de reubicación pozos, de oficinas operativas o administrativas se deberá especificar la nueva dirección,</t>
-  </si>
-  <si>
-    <t>ubicación o nombre del nuevo pozo:</t>
-  </si>
-  <si>
-    <t>Observaciones</t>
-  </si>
-  <si>
-    <t>Emitió</t>
-  </si>
-  <si>
-    <t>Supervisó</t>
-  </si>
-  <si>
-    <t>Vo. Bo.</t>
-  </si>
-  <si>
-    <t>Autorizó</t>
-  </si>
-  <si>
-    <t>Analisata/Supervisor</t>
-  </si>
-  <si>
-    <t>nombre</t>
-  </si>
-  <si>
-    <t>Coordinador Supervisor de Área</t>
-  </si>
-  <si>
-    <t>Coordinador / Supervisor de Infromación Financiera</t>
-  </si>
-  <si>
-    <t>Gerencia Facultad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -334,17 +281,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="MS Mincho"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="MS Gothic"/>
-      <family val="3"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Arial Narrow"/>
@@ -353,6 +289,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
@@ -519,136 +462,132 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -974,8 +913,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:L39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="9.88671875" customWidth="1"/>
@@ -992,406 +931,609 @@
     <col min="14" max="14" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="16.8" customHeight="1">
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="37" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+    </row>
+    <row r="2" spans="1:12" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="38" t="s">
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="38"/>
-    </row>
-    <row r="3" spans="2:12">
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="36" t="s">
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="36"/>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="36" t="s">
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="24"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="36"/>
-      <c r="L4" s="9"/>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="36" t="s">
+      <c r="K4" s="10"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-    </row>
-    <row r="7" spans="2:12" ht="15.6">
-      <c r="C7" s="39" t="s">
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-    </row>
-    <row r="8" spans="2:12" ht="15.6">
-      <c r="C8" s="41" t="s">
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="E10" s="4" t="s">
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="27"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="24"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="24"/>
+      <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="12" spans="2:12">
-      <c r="E12" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="2:12">
-      <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="6" t="s">
+      <c r="D14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="32" t="s">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="24"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="24"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+    </row>
+    <row r="17" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="24"/>
+      <c r="B17" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="1:11" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="24"/>
+      <c r="B18" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="B15" s="10"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="17" spans="2:11" ht="21.6" customHeight="1">
-      <c r="B17" s="24" t="s">
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="24"/>
+      <c r="B19" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-    </row>
-    <row r="18" spans="2:11" ht="22.8" customHeight="1">
-      <c r="B18" s="25" t="s">
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="24"/>
+      <c r="B21" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" spans="2:11" ht="22.2" customHeight="1">
-      <c r="B19" s="25" t="s">
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="24"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+    </row>
+    <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="24"/>
+      <c r="B23" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="30"/>
-    </row>
-    <row r="21" spans="2:11">
-      <c r="B21" s="22" t="s">
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+    </row>
+    <row r="24" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="24"/>
+      <c r="B24" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-    </row>
-    <row r="22" spans="2:11" ht="15.6">
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-    </row>
-    <row r="23" spans="2:11" ht="15.6">
-      <c r="B23" s="23" t="s">
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="6"/>
+    </row>
+    <row r="25" spans="1:11" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="24"/>
+      <c r="B26" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-    </row>
-    <row r="24" spans="2:11" ht="15.6">
-      <c r="B24" s="23" t="s">
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="22"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="24"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="37"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="24"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="37"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="24"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="37"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="24"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="37"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="24"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="40"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="42"/>
-    </row>
-    <row r="25" spans="2:11" ht="4.2" customHeight="1"/>
-    <row r="26" spans="2:11">
-      <c r="B26" s="13" t="s">
+      <c r="D34" s="23"/>
+      <c r="E34" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="15"/>
-    </row>
-    <row r="27" spans="2:11">
-      <c r="B27" s="16"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="18"/>
-    </row>
-    <row r="28" spans="2:11">
-      <c r="B28" s="16"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="18"/>
-    </row>
-    <row r="29" spans="2:11">
-      <c r="B29" s="16"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="18"/>
-    </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="16"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="18"/>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="19"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="21"/>
-    </row>
-    <row r="34" spans="3:10">
-      <c r="C34" s="44" t="s">
+      <c r="F34" s="23"/>
+      <c r="G34" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44" t="s">
+      <c r="H34" s="23"/>
+      <c r="I34" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44" t="s">
+      <c r="J34" s="23"/>
+      <c r="K34" s="24"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="24"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="24"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="24"/>
+    </row>
+    <row r="38" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="24"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J38" s="23"/>
+      <c r="K38" s="24"/>
+    </row>
+    <row r="39" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H34" s="44"/>
-      <c r="I34" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" s="44"/>
-    </row>
-    <row r="35" spans="3:10">
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="45"/>
-    </row>
-    <row r="36" spans="3:10">
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="45"/>
-    </row>
-    <row r="37" spans="3:10">
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
-    </row>
-    <row r="38" spans="3:10" ht="25.8" customHeight="1">
-      <c r="C38" s="12" t="s">
+      <c r="D39" s="23"/>
+      <c r="E39" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J38" s="12"/>
-    </row>
-    <row r="39" spans="3:10" ht="27.6" customHeight="1">
-      <c r="C39" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12" t="s">
+      <c r="H39" s="23"/>
+      <c r="I39" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J39" s="12"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="B26:K26"/>
+    <mergeCell ref="B27:K31"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="B21:K21"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B17:K17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F24:J24"/>
     <mergeCell ref="B2:C5"/>
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="D15:H15"/>
@@ -1403,29 +1545,6 @@
     <mergeCell ref="C7:K7"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="C8:K8"/>
-    <mergeCell ref="B21:K21"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B17:K17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="B26:K26"/>
-    <mergeCell ref="B27:K31"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/database/controller_excel/Baja FO-DSP BAJA.xlsx
+++ b/database/controller_excel/Baja FO-DSP BAJA.xlsx
@@ -239,7 +239,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,13 +292,6 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial Narrow"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -464,7 +457,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -480,6 +473,82 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -487,6 +556,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -501,93 +579,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="4"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" indent="15"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -618,7 +614,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>347345</xdr:colOff>
+      <xdr:colOff>275627</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>149225</xdr:rowOff>
     </xdr:to>
@@ -917,127 +913,126 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.21875" customWidth="1"/>
-    <col min="7" max="7" width="17.88671875" customWidth="1"/>
-    <col min="8" max="8" width="26.88671875" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.5546875" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="9" max="10" width="15.21875" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" customWidth="1"/>
     <col min="12" max="12" width="4.33203125" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:12" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="11" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="12" t="s">
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="12"/>
+      <c r="K2" s="41"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="24"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="10" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="10"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="10" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="10"/>
+      <c r="K4" s="39"/>
       <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="10" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="13" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
     </row>
     <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
-      <c r="B8" s="24"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="43" t="s">
         <v>6</v>
       </c>
@@ -1051,91 +1046,87 @@
       <c r="K8" s="43"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="26" t="s">
+      <c r="A10" s="7"/>
+      <c r="D10" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="27"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29" t="s">
+      <c r="F12" s="14"/>
+      <c r="G12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="24"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
+      <c r="A14" s="7"/>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="9"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="35"/>
       <c r="I14" s="2" t="s">
         <v>11</v>
       </c>
@@ -1147,106 +1138,106 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="24"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="24"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
     </row>
     <row r="17" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24"/>
-      <c r="B17" s="16" t="s">
+      <c r="A17" s="7"/>
+      <c r="B17" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
     </row>
     <row r="18" spans="1:11" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
-      <c r="B18" s="17" t="s">
+      <c r="A18" s="7"/>
+      <c r="B18" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="32"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="13"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
-      <c r="B19" s="17" t="s">
+      <c r="A19" s="7"/>
+      <c r="B19" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
-      <c r="B21" s="14" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="24"/>
+      <c r="A22" s="7"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -1259,262 +1250,278 @@
       <c r="K22" s="5"/>
     </row>
     <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="24"/>
-      <c r="B23" s="15" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
     </row>
     <row r="24" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="24"/>
-      <c r="B24" s="15" t="s">
+      <c r="A24" s="7"/>
+      <c r="B24" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
       <c r="K24" s="6"/>
     </row>
     <row r="25" spans="1:11" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="24"/>
-      <c r="B26" s="20" t="s">
+      <c r="A26" s="7"/>
+      <c r="B26" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="22"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="18"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="24"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="37"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="21"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="24"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="37"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="21"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="24"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="37"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="21"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="24"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="37"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="21"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="24"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="40"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="24"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="24"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="24"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="24"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="23" t="s">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23" t="s">
+      <c r="D34" s="15"/>
+      <c r="E34" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23" t="s">
+      <c r="F34" s="15"/>
+      <c r="G34" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23" t="s">
+      <c r="H34" s="15"/>
+      <c r="I34" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="23"/>
-      <c r="K34" s="24"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="24"/>
-      <c r="B35" s="24"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="24"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="7"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="24"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="24"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="24"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="24"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="7"/>
     </row>
     <row r="38" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="24"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="23" t="s">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23" t="s">
+      <c r="D38" s="15"/>
+      <c r="E38" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23" t="s">
+      <c r="F38" s="15"/>
+      <c r="G38" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23" t="s">
+      <c r="H38" s="15"/>
+      <c r="I38" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J38" s="23"/>
-      <c r="K38" s="24"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="7"/>
     </row>
     <row r="39" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="24"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="23" t="s">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23" t="s">
+      <c r="D39" s="15"/>
+      <c r="E39" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23" t="s">
+      <c r="F39" s="15"/>
+      <c r="G39" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23" t="s">
+      <c r="H39" s="15"/>
+      <c r="I39" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="J39" s="23"/>
-      <c r="K39" s="24"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B2:C5"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D2:I4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="B17:K17"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:J24"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B21:K21"/>
+    <mergeCell ref="B23:K23"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="E39:F39"/>
     <mergeCell ref="G39:H39"/>
@@ -1525,26 +1532,10 @@
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="G34:H34"/>
     <mergeCell ref="I34:J34"/>
-    <mergeCell ref="B21:K21"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B17:K17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="B2:C5"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D2:I4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C38:D38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/database/controller_excel/Baja FO-DSP BAJA.xlsx
+++ b/database/controller_excel/Baja FO-DSP BAJA.xlsx
@@ -457,7 +457,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -495,6 +495,60 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="15"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="5"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,66 +578,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="15"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -941,66 +935,66 @@
     </row>
     <row r="2" spans="1:12" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="40" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="41" t="s">
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="41"/>
+      <c r="K2" s="24"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="39" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="39"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="39" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="39"/>
+      <c r="K4" s="22"/>
       <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="39" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
@@ -1018,32 +1012,32 @@
     <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
     </row>
     <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
@@ -1060,14 +1054,14 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
       <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -1120,13 +1114,13 @@
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="35"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
       <c r="I14" s="2" t="s">
         <v>11</v>
       </c>
@@ -1141,11 +1135,11 @@
       <c r="A15" s="7"/>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="38"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -1165,28 +1159,28 @@
     </row>
     <row r="17" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
     </row>
     <row r="18" spans="1:11" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="21"/>
       <c r="G18" s="13"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -1195,13 +1189,13 @@
     </row>
     <row r="19" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="21"/>
       <c r="G19" s="13"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -1223,18 +1217,18 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
@@ -1251,32 +1245,32 @@
     </row>
     <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
     </row>
     <row r="24" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
       <c r="K24" s="6"/>
     </row>
     <row r="25" spans="1:11" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1294,83 +1288,83 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="18"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="36"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="21"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="39"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="7"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="21"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="39"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="7"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="21"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="39"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="21"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="39"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="7"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="24"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="42"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
@@ -1401,22 +1395,22 @@
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15" t="s">
+      <c r="D34" s="33"/>
+      <c r="E34" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15" t="s">
+      <c r="F34" s="33"/>
+      <c r="G34" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15" t="s">
+      <c r="H34" s="33"/>
+      <c r="I34" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="15"/>
+      <c r="J34" s="33"/>
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -1461,67 +1455,47 @@
     <row r="38" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15" t="s">
+      <c r="D38" s="33"/>
+      <c r="E38" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15" t="s">
+      <c r="F38" s="33"/>
+      <c r="G38" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15" t="s">
+      <c r="H38" s="33"/>
+      <c r="I38" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="J38" s="15"/>
+      <c r="J38" s="33"/>
       <c r="K38" s="7"/>
     </row>
     <row r="39" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15" t="s">
+      <c r="D39" s="33"/>
+      <c r="E39" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15" t="s">
+      <c r="F39" s="33"/>
+      <c r="G39" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15" t="s">
+      <c r="H39" s="33"/>
+      <c r="I39" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="J39" s="15"/>
+      <c r="J39" s="33"/>
       <c r="K39" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B2:C5"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D2:I4"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="B17:K17"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:J24"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B21:K21"/>
-    <mergeCell ref="B23:K23"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="E39:F39"/>
     <mergeCell ref="G39:H39"/>
@@ -1536,6 +1510,26 @@
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B17:K17"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:J24"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B21:K21"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="B2:C5"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D2:I4"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="D10:I10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
